--- a/data/trans_orig/P16A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62409</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>90176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127914</t>
+          <t>129397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132746</t>
+          <t>131057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179097</t>
+          <t>178991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969314</t>
+          <t>968780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>995714</t>
+          <t>996205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1187199</t>
+          <t>1185716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1227840</t>
+          <t>1224937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2167738</t>
+          <t>2167844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2214089</t>
+          <t>2215778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>46597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73769</t>
+          <t>75472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>66253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105587</t>
+          <t>103075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655169</t>
+          <t>1656929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1675623</t>
+          <t>1676903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1513904</t>
+          <t>1512201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1542151</t>
+          <t>1541076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3174480</t>
+          <t>3176992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3211437</t>
+          <t>3213814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39708</t>
+          <t>39940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528791</t>
+          <t>527967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543916</t>
+          <t>544193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454098</t>
+          <t>454381</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469133</t>
+          <t>469601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988112</t>
+          <t>987880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1009497</t>
+          <t>1009650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>103312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155861</t>
+          <t>155481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207406</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235596</t>
+          <t>233080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301929</t>
+          <t>297133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3170464</t>
+          <t>3172213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3207315</t>
+          <t>3207718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3171791</t>
+          <t>3171745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3223336</t>
+          <t>3223716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6352793</t>
+          <t>6357589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6419126</t>
+          <t>6421642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69653</t>
+          <t>66557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124773</t>
+          <t>124027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170796</t>
+          <t>168739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>169791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227253</t>
+          <t>226839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>904175</t>
+          <t>907271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>935445</t>
+          <t>937469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1162944</t>
+          <t>1165001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1208967</t>
+          <t>1209713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2080315</t>
+          <t>2080729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2136993</t>
+          <t>2137777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72398</t>
+          <t>72015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111447</t>
+          <t>110992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115776</t>
+          <t>117714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165741</t>
+          <t>166317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1895677</t>
+          <t>1893384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1925058</t>
+          <t>1923436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1640371</t>
+          <t>1640826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1679420</t>
+          <t>1679803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3546099</t>
+          <t>3545523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3596064</t>
+          <t>3594126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>26117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>21753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46668</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452214</t>
+          <t>451830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472863</t>
+          <t>472671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430376</t>
+          <t>431537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447448</t>
+          <t>447419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891318</t>
+          <t>891446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>917444</t>
+          <t>916233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93928</t>
+          <t>92701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141185</t>
+          <t>140391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222978</t>
+          <t>223635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287626</t>
+          <t>289398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330466</t>
+          <t>334621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412330</t>
+          <t>409433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3272997</t>
+          <t>3273791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3320254</t>
+          <t>3321481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3255587</t>
+          <t>3253815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3320235</t>
+          <t>3319578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6545065</t>
+          <t>6547962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6626929</t>
+          <t>6622774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51089</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104893</t>
+          <t>105066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>149605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140534</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189780</t>
+          <t>188407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>703957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>726160</t>
+          <t>727025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>846374</t>
+          <t>845055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>889767</t>
+          <t>889594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1559227</t>
+          <t>1560600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1608473</t>
+          <t>1607264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83135</t>
+          <t>82485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109037</t>
+          <t>108459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154044</t>
+          <t>152549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168669</t>
+          <t>170299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>225908</t>
+          <t>224961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1993250</t>
+          <t>1993900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2025776</t>
+          <t>2025892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1834256</t>
+          <t>1835751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1879263</t>
+          <t>1879841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3838777</t>
+          <t>3839724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3896016</t>
+          <t>3894386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521442</t>
+          <t>522442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538179</t>
+          <t>538517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525192</t>
+          <t>525640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541608</t>
+          <t>541656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1055293</t>
+          <t>1054987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078244</t>
+          <t>1076957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96907</t>
+          <t>98844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139321</t>
+          <t>141428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238967</t>
+          <t>237089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301785</t>
+          <t>301298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351175</t>
+          <t>352521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430577</t>
+          <t>431323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3238297</t>
+          <t>3236190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3280711</t>
+          <t>3278774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3230315</t>
+          <t>3230802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3293133</t>
+          <t>3295011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6479141</t>
+          <t>6478395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6558543</t>
+          <t>6557197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56213</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120428</t>
+          <t>119169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154412</t>
+          <t>155766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159647</t>
+          <t>159354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202732</t>
+          <t>201538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457239</t>
+          <t>456869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480488</t>
+          <t>480373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>596701</t>
+          <t>595347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630685</t>
+          <t>631944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1061833</t>
+          <t>1063027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1104918</t>
+          <t>1105211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>55197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105732</t>
+          <t>102499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94921</t>
+          <t>98167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159846</t>
+          <t>157596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>168841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252400</t>
+          <t>248993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2184595</t>
+          <t>2187828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2233845</t>
+          <t>2235130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2077299</t>
+          <t>2079549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2142224</t>
+          <t>2138978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4275072</t>
+          <t>4278479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4351812</t>
+          <t>4358631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621786</t>
+          <t>621767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636960</t>
+          <t>636724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629665</t>
+          <t>630126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>644927</t>
+          <t>645610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258185</t>
+          <t>1259461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279431</t>
+          <t>1279312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109253</t>
+          <t>109703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168898</t>
+          <t>168625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>240087</t>
+          <t>244182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>325034</t>
+          <t>326008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374744</t>
+          <t>371949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480565</t>
+          <t>482741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3281504</t>
+          <t>3281777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3341149</t>
+          <t>3340699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3323687</t>
+          <t>3322713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3408634</t>
+          <t>3404539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6618559</t>
+          <t>6616383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6724380</t>
+          <t>6727175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62943</t>
+          <t>60346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90176</t>
+          <t>88494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129397</t>
+          <t>128729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131057</t>
+          <t>131767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178991</t>
+          <t>178188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>968780</t>
+          <t>971377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>996205</t>
+          <t>997056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1185716</t>
+          <t>1186384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1224937</t>
+          <t>1226619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2167844</t>
+          <t>2168647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2215778</t>
+          <t>2215068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75472</t>
+          <t>75664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103075</t>
+          <t>104301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1656929</t>
+          <t>1656146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676903</t>
+          <t>1676409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1512201</t>
+          <t>1512009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1541076</t>
+          <t>1542292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3176992</t>
+          <t>3175766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3213814</t>
+          <t>3214015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527967</t>
+          <t>529211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544193</t>
+          <t>544208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454381</t>
+          <t>454972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469601</t>
+          <t>469012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>987880</t>
+          <t>988547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1009650</t>
+          <t>1009892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207452</t>
+          <t>205573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233080</t>
+          <t>232017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>294823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3172213</t>
+          <t>3170629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3207718</t>
+          <t>3206292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3171745</t>
+          <t>3173624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3223716</t>
+          <t>3226168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6357589</t>
+          <t>6359899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6421642</t>
+          <t>6422705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66557</t>
+          <t>68802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124027</t>
+          <t>126299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168739</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169791</t>
+          <t>169173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226839</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>907271</t>
+          <t>905026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>937469</t>
+          <t>937625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1165001</t>
+          <t>1161142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1209713</t>
+          <t>1207441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2080729</t>
+          <t>2082373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2137777</t>
+          <t>2138395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>65621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72015</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110992</t>
+          <t>111821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117714</t>
+          <t>117420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166317</t>
+          <t>164909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1893384</t>
+          <t>1894401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1923436</t>
+          <t>1924407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1640826</t>
+          <t>1639997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1679803</t>
+          <t>1679876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3545523</t>
+          <t>3546931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3594126</t>
+          <t>3594420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451830</t>
+          <t>453043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472671</t>
+          <t>472743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431537</t>
+          <t>432249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447419</t>
+          <t>448410</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891446</t>
+          <t>891618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916233</t>
+          <t>916249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>93771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140391</t>
+          <t>138864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223635</t>
+          <t>222892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289398</t>
+          <t>286053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>334621</t>
+          <t>329202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409433</t>
+          <t>409903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3273791</t>
+          <t>3275318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3321481</t>
+          <t>3320411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3253815</t>
+          <t>3257160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3319578</t>
+          <t>3320321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6547962</t>
+          <t>6547492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6622774</t>
+          <t>6628193</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105066</t>
+          <t>104852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>149992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141743</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188407</t>
+          <t>190312</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>703957</t>
+          <t>703208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>727025</t>
+          <t>726830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>845055</t>
+          <t>844668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>889594</t>
+          <t>889808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1560600</t>
+          <t>1558695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1607264</t>
+          <t>1609441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>51537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>83622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108459</t>
+          <t>107600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152549</t>
+          <t>152151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170299</t>
+          <t>166307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224961</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1993900</t>
+          <t>1992763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2025892</t>
+          <t>2024848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1835751</t>
+          <t>1836149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1879841</t>
+          <t>1880700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3839724</t>
+          <t>3841407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3894386</t>
+          <t>3898378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24444</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522442</t>
+          <t>522453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538517</t>
+          <t>538783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525640</t>
+          <t>526647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541656</t>
+          <t>541948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054987</t>
+          <t>1054606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076957</t>
+          <t>1076867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98844</t>
+          <t>97214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141428</t>
+          <t>141966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237089</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301298</t>
+          <t>304094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352521</t>
+          <t>350284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431323</t>
+          <t>425110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236190</t>
+          <t>3235652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3278774</t>
+          <t>3280404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3230802</t>
+          <t>3228006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3295011</t>
+          <t>3294410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6478395</t>
+          <t>6484608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6557197</t>
+          <t>6559434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135395</t>
+          <t>143750</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119169</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155766</t>
+          <t>160743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>178804</t>
+          <t>191600</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159354</t>
+          <t>173317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201538</t>
+          <t>213315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>470043</t>
+          <t>529197</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456869</t>
+          <t>516654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>480373</t>
+          <t>540476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>615718</t>
+          <t>675357</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>595347</t>
+          <t>658364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631944</t>
+          <t>691288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1085761</t>
+          <t>1204554</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1063027</t>
+          <t>1182839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1105211</t>
+          <t>1222837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751113</t>
+          <t>819107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751113</t>
+          <t>819107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751113</t>
+          <t>819107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264565</t>
+          <t>1396154</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264565</t>
+          <t>1396154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264565</t>
+          <t>1396154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>86634</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55197</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102499</t>
+          <t>108025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,67 +5915,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>133316</t>
+          <t>145546</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98167</t>
+          <t>128448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157596</t>
+          <t>165578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>232179</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>207667</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>262272</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>5,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>215726</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>168841</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>248993</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2207916</t>
+          <t>2143932</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2187828</t>
+          <t>2122541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2235130</t>
+          <t>2160631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,67 +6028,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2103829</t>
+          <t>2025161</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2079549</t>
+          <t>2005129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2138978</t>
+          <t>2042259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,37%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4597</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4169095</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4139002</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4193607</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4311746</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4278479</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4358631</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>40080</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>51818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>630729</t>
+          <t>695630</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621767</t>
+          <t>686652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636724</t>
+          <t>702126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>638877</t>
+          <t>710754</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630126</t>
+          <t>701522</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645610</t>
+          <t>717468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1269606</t>
+          <t>1406384</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1259461</t>
+          <t>1394646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279312</t>
+          <t>1416313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109703</t>
+          <t>129390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168625</t>
+          <t>176938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>290297</t>
+          <t>313418</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244182</t>
+          <t>286810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326008</t>
+          <t>339713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>432011</t>
+          <t>463859</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371949</t>
+          <t>427780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>482741</t>
+          <t>499560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3308688</t>
+          <t>3368760</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3281777</t>
+          <t>3342262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3340699</t>
+          <t>3389810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3358424</t>
+          <t>3411273</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3322713</t>
+          <t>3384978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3404539</t>
+          <t>3437881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6667113</t>
+          <t>6780033</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6616383</t>
+          <t>6744332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6727175</t>
+          <t>6816112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648721</t>
+          <t>3724691</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648721</t>
+          <t>3724691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648721</t>
+          <t>3724691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099124</t>
+          <t>7243892</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099124</t>
+          <t>7243892</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099124</t>
+          <t>7243892</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
